--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" t="str">
-        <v>2.707</v>
+        <v>20.534</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>14.448</v>
+        <v>2.353</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.353</v>
+        <v>5.470</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.470</v>
+        <v>2.822</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>5.588</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>2.565</v>
+        <v>5.110</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>5.110</v>
+        <v>3.092</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>6.350</v>
+        <v>3.185</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>6.237</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>6.210</v>
+        <v>2.752</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>2.752</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>3.222</v>
+        <v>5.999</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>5.999</v>
+        <v>5.880</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>2.912</v>
+        <v>5.879</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -776,7 +776,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>5.879</v>
+        <v>5.330</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="str">
-        <v>5.330</v>
+        <v>7.833</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>7.833</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>2.403</v>
+        <v>2.705</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>2.705</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>2.711</v>
+        <v>7.213</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -896,7 +896,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>5.551</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>4.856</v>
+        <v>2.276</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.247</v>
+        <v>2.659</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>2.276</v>
+        <v>4.937</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>2.659</v>
+        <v>5.557</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>5.087</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.557</v>
+        <v>2.378</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1033,10 +1033,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.935</v>
+        <v>4.634</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>2.378</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.396</v>
+        <v>5.610</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>NOCCIOLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1093,10 +1093,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>8.327</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1116,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.977</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.392</v>
+        <v>2.493</v>
       </c>
     </row>
     <row r="38">
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="str">
-        <v>25.038</v>
+        <v>21.856</v>
       </c>
     </row>
     <row r="39">
@@ -1256,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="F43" t="str">
-        <v>16.653</v>
+        <v>16.658</v>
       </c>
     </row>
     <row r="44">
@@ -1313,10 +1313,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>5.656</v>
+        <v>2.837</v>
       </c>
     </row>
     <row r="47">
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" t="str">
-        <v>5.301</v>
+        <v>8.065</v>
       </c>
     </row>
     <row r="49">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.873</v>
+        <v>750</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>750</v>
+        <v>3.053</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>MONT BLANC</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>3.053</v>
+        <v>3.275</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>6.718</v>
+        <v>2.675</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54" t="str">
-        <v>2.675</v>
+        <v>2.670</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1496,32 +1496,12 @@
         <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>1.076</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B56" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E56" t="str">
-        <v>2</v>
-      </c>
-      <c r="F56" t="str">
         <v>5.842</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F55"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="str">
-        <v>20.534</v>
+        <v>17.642</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -516,7 +516,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>2.353</v>
+        <v>2.820</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>5.470</v>
+        <v>5.905</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -556,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>2.822</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>2.565</v>
+        <v>6.333</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>5.110</v>
+        <v>3.185</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>3.092</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -636,7 +636,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.185</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.989</v>
+        <v>2.940</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>2.752</v>
+        <v>5.880</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.222</v>
+        <v>3.113</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -716,7 +716,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>5.999</v>
+        <v>5.172</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="str">
-        <v>5.880</v>
+        <v>7.689</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -756,7 +756,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>5.879</v>
+        <v>5.020</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>5.330</v>
+        <v>2.705</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>7.833</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.403</v>
+        <v>4.747</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>2.705</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FIORDILATTE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>5.607</v>
+        <v>2.276</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="str">
-        <v>7.213</v>
+        <v>4.937</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>4.756</v>
+        <v>2.838</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.276</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.659</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIMONE</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>4.937</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>5.557</v>
+        <v>5.760</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.935</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>PERA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.378</v>
+        <v>2.377</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1033,10 +1033,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>4.634</v>
+        <v>2.493</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MIRTILLO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F33" t="str">
-        <v>2.427</v>
+        <v>19.767</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>NOCCIOLA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>5.610</v>
+        <v>3.139</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.977</v>
+        <v>2.879</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F36" t="str">
-        <v>2.392</v>
+        <v>13.858</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>YOGURT</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>2.493</v>
+        <v>5.688</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>21.856</v>
+        <v>2.837</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>POLLICINA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>3.137</v>
+        <v>3.107</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>3.139</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1216,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>2.809</v>
+        <v>2.521</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>SEADAS</v>
+        <v>SEMIFREDDO  TIRAMISU</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1236,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.879</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>STRACCIATELLA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>16.658</v>
+        <v>3.327</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>YOGURT</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.927</v>
+        <v>1.001</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>3.052</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.837</v>
+        <v>2.675</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SACRIPANTE</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F47" t="str">
-        <v>3.107</v>
+        <v>3.717</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,155 +1353,15 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>8.065</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B49" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E49" t="str">
-        <v>1</v>
-      </c>
-      <c r="F49" t="str">
-        <v>1.017</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B50" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E50" t="str">
-        <v>1</v>
-      </c>
-      <c r="F50" t="str">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B51" t="str">
-        <v>MONT BLANC</v>
-      </c>
-      <c r="C51" t="str">
-        <v/>
-      </c>
-      <c r="D51" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E51" t="str">
-        <v>1</v>
-      </c>
-      <c r="F51" t="str">
-        <v>3.053</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B52" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E52" t="str">
-        <v>1</v>
-      </c>
-      <c r="F52" t="str">
-        <v>3.275</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B53" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E53" t="str">
-        <v>1</v>
-      </c>
-      <c r="F53" t="str">
-        <v>2.675</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B54" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E54" t="str">
-        <v>5</v>
-      </c>
-      <c r="F54" t="str">
-        <v>2.670</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B55" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E55" t="str">
-        <v>2</v>
-      </c>
-      <c r="F55" t="str">
         <v>5.842</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ALBICOCCA</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>1.608</v>
+        <v>1.817</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -456,7 +456,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>2.208</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>2.160</v>
+        <v>2.898</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>17.642</v>
+        <v>5.731</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="str">
-        <v>2.820</v>
+        <v>15.057</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BIANCANEVE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>5.905</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.542</v>
+        <v>4.584</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -576,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>6.333</v>
+        <v>5.455</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CACHI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>3.185</v>
+        <v>2.110</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.989</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="str">
-        <v>3.222</v>
+        <v>9.002</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>2.940</v>
+        <v>6.040</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>5.880</v>
+        <v>3.037</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.113</v>
+        <v>3.057</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.172</v>
+        <v>3.054</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>7.689</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -756,7 +756,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>5.020</v>
+        <v>5.762</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.705</v>
+        <v>6.135</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>5.607</v>
+        <v>2.741</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>4.747</v>
+        <v>2.613</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>4.756</v>
+        <v>2.629</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.276</v>
+        <v>3.230</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LIMONE</v>
+        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>4.937</v>
+        <v>3.041</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>2.838</v>
+        <v>8.614</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="str">
-        <v>2.935</v>
+        <v>8.846</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>2.238</v>
+        <v>3.003</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MIRTILLO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>2.427</v>
+        <v>7.292</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>NOCCIOLA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>5.760</v>
+        <v>2.687</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.977</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>PERA</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.377</v>
+        <v>3.050</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.493</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>19.767</v>
+        <v>5.229</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>3.139</v>
+        <v>2.686</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>SEADAS</v>
+        <v>MORA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.879</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>STRACCIATELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>13.858</v>
+        <v>9.065</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>YOGURT</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" t="str">
-        <v>5.688</v>
+        <v>11.708</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>2.837</v>
+        <v>9.763</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>SACRIPANTE</v>
+        <v>PERA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>3.107</v>
+        <v>2.160</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.376</v>
+        <v>2.292</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F41" t="str">
-        <v>2.521</v>
+        <v>13.814</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>SEMIFREDDO  TIRAMISU</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1236,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>750</v>
+        <v>2.700</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>MONT BLANC</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>3.327</v>
+        <v>5.710</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>1.001</v>
+        <v>3.080</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F45" t="str">
-        <v>6.708</v>
+        <v>19.859</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.675</v>
+        <v>2.585</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>3.717</v>
+        <v>2.629</v>
       </c>
     </row>
     <row r="48">
@@ -1344,24 +1344,304 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
+        <v>ZABAIONE GELATO</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E48" t="str">
+        <v>1</v>
+      </c>
+      <c r="F48" t="str">
+        <v>3.315</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B49" t="str">
+        <v>SACRIPANTE</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E49" t="str">
+        <v>1</v>
+      </c>
+      <c r="F49" t="str">
+        <v>3.151</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B50" t="str">
+        <v>BUONGIORNO AMORE</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E50" t="str">
+        <v>1</v>
+      </c>
+      <c r="F50" t="str">
+        <v>2.591</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B51" t="str">
+        <v>TE VERDE MATCHA</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2</v>
+      </c>
+      <c r="F51" t="str">
+        <v>5.346</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B52" t="str">
+        <v>CARROT CAKE</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E52" t="str">
+        <v>1</v>
+      </c>
+      <c r="F52" t="str">
+        <v>2.680</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B53" t="str">
+        <v>PISTACCHIO SIRIANO</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E53" t="str">
+        <v>4</v>
+      </c>
+      <c r="F53" t="str">
+        <v>11.924</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B54" t="str">
+        <v>FIOR DI CIOCCOLATO</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E54" t="str">
+        <v>1</v>
+      </c>
+      <c r="F54" t="str">
+        <v>2.771</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B55" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E55" t="str">
+        <v>1</v>
+      </c>
+      <c r="F55" t="str">
+        <v>3.038</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B56" t="str">
+        <v>MONT BLANC</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E56" t="str">
+        <v>1</v>
+      </c>
+      <c r="F56" t="str">
+        <v>3.300</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B57" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E57" t="str">
+        <v>1</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2.807</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B58" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E58" t="str">
+        <v>1</v>
+      </c>
+      <c r="F58" t="str">
+        <v>2.827</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B59" t="str">
+        <v>CASTAGNA AL WHISKY</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E59" t="str">
+        <v>1</v>
+      </c>
+      <c r="F59" t="str">
+        <v>2.047</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B60" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2.586</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B61" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E61" t="str">
+        <v>3</v>
+      </c>
+      <c r="F61" t="str">
+        <v>1.556</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B62" t="str">
         <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="D48" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E48" t="str">
-        <v>2</v>
-      </c>
-      <c r="F48" t="str">
-        <v>5.842</v>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E62" t="str">
+        <v>1</v>
+      </c>
+      <c r="F62" t="str">
+        <v>3.083</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F62"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -424,7 +424,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ALBICOCCA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>1.817</v>
+        <v>2.505</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>2.398</v>
+        <v>2.442</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>2.898</v>
+        <v>5.702</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>5.731</v>
+        <v>26.847</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>15.057</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BAKLAVA</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>3.018</v>
+        <v>5.509</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BANANA E LIME</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -556,7 +556,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>4.584</v>
+        <v>5.443</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -576,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>5.455</v>
+        <v>5.537</v>
       </c>
     </row>
     <row r="10">
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>2.110</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.444</v>
+        <v>2.856</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>9.002</v>
+        <v>5.986</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>6.040</v>
+        <v>3.001</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="str">
-        <v>3.037</v>
+        <v>9.090</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>3.057</v>
+        <v>2.767</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>3.054</v>
+        <v>5.242</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.988</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>5.762</v>
+        <v>2.527</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>6.135</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.741</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -816,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.613</v>
+        <v>2.764</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>2.629</v>
+        <v>3.106</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>3.230</v>
+        <v>2.961</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FINOCCHIO MIELE LIQUIRIZIA</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>3.041</v>
+        <v>9.853</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>8.614</v>
+        <v>4.526</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>8.846</v>
+        <v>2.896</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>3.003</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIMONE</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -956,7 +956,7 @@
         <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>7.292</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>2.687</v>
+        <v>5.044</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>2.694</v>
+        <v>5.537</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>3.050</v>
+        <v>2.722</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.883</v>
+        <v>2.639</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>5.229</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>2.686</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MORA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1093,10 +1093,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.411</v>
+        <v>5.634</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>9.065</v>
+        <v>3.130</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>11.708</v>
+        <v>2.652</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>9.763</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="39">
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.160</v>
+        <v>2.481</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>2.292</v>
+        <v>5.645</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>13.814</v>
+        <v>2.363</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>POLLICINA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F42" t="str">
-        <v>2.700</v>
+        <v>23.038</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>5.710</v>
+        <v>5.482</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>SEADAS</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>3.080</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>STRACCIATELLA</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>19.859</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>TIRAMISU'</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.585</v>
+        <v>3.101</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>YOGURT</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F47" t="str">
-        <v>2.629</v>
+        <v>16.691</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>3.315</v>
+        <v>2.692</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>SACRIPANTE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>3.151</v>
+        <v>5.546</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.591</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>5.346</v>
+        <v>5.502</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>CARROT CAKE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.680</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>11.924</v>
+        <v>2.982</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.771</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>3.038</v>
+        <v>2.887</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>MONT BLANC</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1516,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>3.300</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.807</v>
+        <v>2.746</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>2.827</v>
+        <v>3.169</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F59" t="str">
-        <v>2.047</v>
+        <v>3.076</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.586</v>
+        <v>2.965</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1613,10 +1613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>1.556</v>
+        <v>2.959</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>3.083</v>
+        <v>5.658</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.505</v>
+        <v>2.435</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -456,7 +456,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>2.442</v>
+        <v>2.403</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>5.702</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5" t="str">
-        <v>26.847</v>
+        <v>6.791</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F6" t="str">
-        <v>2.396</v>
+        <v>24.088</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>5.509</v>
+        <v>2.266</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.443</v>
+        <v>2.884</v>
       </c>
     </row>
     <row r="9">
@@ -576,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="str">
-        <v>5.537</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CACHI</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>2.022</v>
+        <v>7.408</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.856</v>
+        <v>2.946</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>5.986</v>
+        <v>2.750</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>3.001</v>
+        <v>2.869</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>9.090</v>
+        <v>3.049</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>2.767</v>
+        <v>12.002</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -716,7 +716,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>5.242</v>
+        <v>5.756</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA AGNESE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="str">
-        <v>2.444</v>
+        <v>8.701</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>2.527</v>
+        <v>5.240</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.681</v>
+        <v>5.340</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>2.708</v>
+        <v>5.326</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -816,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.764</v>
+        <v>2.616</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>ESTASI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>3.106</v>
+        <v>2.819</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FIORDILATTE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.961</v>
+        <v>3.096</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FRAGOLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="str">
-        <v>9.853</v>
+        <v>14.372</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>4.526</v>
+        <v>14.049</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>GIANDUIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.896</v>
+        <v>2.078</v>
       </c>
     </row>
     <row r="27">
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>2.009</v>
+        <v>4.519</v>
       </c>
     </row>
     <row r="28">
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>7.884</v>
+        <v>5.668</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMONE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>5.044</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LIMONE</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" t="str">
-        <v>5.537</v>
+        <v>10.405</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.722</v>
+        <v>2.752</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.639</v>
+        <v>2.950</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MIRTILLO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" t="str">
-        <v>2.562</v>
+        <v>10.636</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.977</v>
+        <v>4.830</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>NOCCIOLA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>5.634</v>
+        <v>4.723</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>3.130</v>
+        <v>6.125</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F37" t="str">
-        <v>2.652</v>
+        <v>15.046</v>
       </c>
     </row>
     <row r="38">
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.624</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PERA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>2.481</v>
+        <v>4.769</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PERA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.645</v>
+        <v>2.789</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1216,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>2.363</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>23.038</v>
+        <v>4.680</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>POLLICINA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F43" t="str">
-        <v>5.482</v>
+        <v>20.542</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.737</v>
+        <v>2.860</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.742</v>
+        <v>2.801</v>
       </c>
     </row>
     <row r="46">
@@ -1313,10 +1313,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>3.101</v>
+        <v>5.308</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>16.691</v>
+        <v>2.858</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F48" t="str">
-        <v>2.692</v>
+        <v>22.695</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>YOGURT</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>5.546</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>3.029</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>5.502</v>
+        <v>3.187</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>PENSIERO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1433,10 +1433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.916</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="53">
@@ -1456,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>2.982</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>CARROT CAKE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" t="str">
-        <v>2.592</v>
+        <v>8.781</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>CIOCCOLATA CALDA FONDENTE</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.887</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>2.646</v>
+        <v>6.010</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>SACHER TORTE</v>
+        <v>PASTIERA NAPOLETANA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.746</v>
+        <v>2.753</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>ZABAIONE AL SAKE'</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>3.169</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>3.076</v>
+        <v>1.075</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.965</v>
+        <v>3.123</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1613,10 +1613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>2.959</v>
+        <v>5.523</v>
       </c>
     </row>
     <row r="62">
@@ -1624,24 +1624,124 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5.616</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B63" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E63" t="str">
+        <v>4</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2.056</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B64" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E64" t="str">
+        <v>1</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2.793</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B65" t="str">
         <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="D62" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E62" t="str">
-        <v>2</v>
-      </c>
-      <c r="F62" t="str">
-        <v>5.658</v>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5.792</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B66" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E66" t="str">
+        <v>4</v>
+      </c>
+      <c r="F66" t="str">
+        <v>11.341</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E67" t="str">
+        <v>1</v>
+      </c>
+      <c r="F67" t="str">
+        <v>2.851</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ALBICOCCA</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.435</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>2.403</v>
+        <v>4.916</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>5.616</v>
+        <v>7.790</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>6.791</v>
+        <v>7.905</v>
       </c>
     </row>
     <row r="6">
@@ -516,7 +516,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="str">
-        <v>24.088</v>
+        <v>23.555</v>
       </c>
     </row>
     <row r="7">
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>2.266</v>
+        <v>4.545</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -556,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>2.884</v>
+        <v>3.030</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>5.508</v>
+        <v>12.197</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>7.408</v>
+        <v>5.548</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>2.946</v>
+        <v>3.400</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <v>2.750</v>
+        <v>15.521</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>2.869</v>
+        <v>2.876</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -676,7 +676,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.049</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>12.002</v>
+        <v>5.837</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.756</v>
+        <v>2.992</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>8.701</v>
+        <v>2.775</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>5.240</v>
+        <v>3.127</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19" t="str">
-        <v>5.340</v>
+        <v>14.789</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>5.326</v>
+        <v>2.780</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>2.616</v>
+        <v>5.400</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>2.819</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>3.096</v>
+        <v>5.431</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>14.372</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>14.049</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>ESTASI</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>2.078</v>
+        <v>6.330</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>4.519</v>
+        <v>11.329</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" t="str">
-        <v>5.668</v>
+        <v>10.506</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LEMON CURD</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>2.609</v>
+        <v>9.094</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>10.405</v>
+        <v>3.008</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>2.752</v>
+        <v>5.372</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1033,10 +1033,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F32" t="str">
-        <v>2.950</v>
+        <v>15.196</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>10.636</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDARINO</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>4.830</v>
+        <v>2.524</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MIRTILLO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>4.723</v>
+        <v>5.749</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>6.125</v>
+        <v>2.827</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F37" t="str">
-        <v>15.046</v>
+        <v>4.786</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PAPAYA</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1156,7 +1156,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>5.337</v>
+        <v>5.681</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PASSION FRUIT</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>4.769</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>2.789</v>
+        <v>6.275</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F41" t="str">
-        <v>2.607</v>
+        <v>23.832</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>4.680</v>
+        <v>3.071</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>20.542</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>POLLICINA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>2.860</v>
+        <v>4.673</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PERA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.801</v>
+        <v>5.326</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.308</v>
+        <v>5.772</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SEADAS</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1336,7 +1336,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>2.858</v>
+        <v>2.467</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>22.695</v>
+        <v>3.038</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>UVA E NOCI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>2.297</v>
+        <v>5.993</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PENSIERO</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>2.461</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SACRIPANTE</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>3.187</v>
+        <v>2.809</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1433,10 +1433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>5.334</v>
+        <v>2.942</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.603</v>
+        <v>5.864</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>8.781</v>
+        <v>2.963</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>CIOCCOLATA CALDA FONDENTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F55" t="str">
-        <v>1.031</v>
+        <v>34.709</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1516,7 +1516,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>6.010</v>
+        <v>5.601</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.753</v>
+        <v>2.090</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>ZABAIONE AL SAKE'</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>3.287</v>
+        <v>3.055</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" t="str">
-        <v>1.075</v>
+        <v>8.680</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.123</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>SACHER TORTE</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>2</v>
       </c>
       <c r="F61" t="str">
-        <v>5.523</v>
+        <v>5.966</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>5.616</v>
+        <v>2.617</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1653,10 +1653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E63" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.056</v>
+        <v>2.879</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.793</v>
+        <v>3.128</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>5.792</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1713,10 +1713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>11.341</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="67">
@@ -1724,24 +1724,264 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E67" t="str">
+        <v>1</v>
+      </c>
+      <c r="F67" t="str">
+        <v>3.162</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B68" t="str">
+        <v>MONT BLANC</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E68" t="str">
+        <v>1</v>
+      </c>
+      <c r="F68" t="str">
+        <v>3.075</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B69" t="str">
+        <v>PASTIERA NAPOLETANA</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E69" t="str">
+        <v>1</v>
+      </c>
+      <c r="F69" t="str">
+        <v>3.128</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E70" t="str">
+        <v>1</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2.853</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>6.171</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" t="str">
+        <v>6.641</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B73" t="str">
+        <v>SACHER TORTE</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2</v>
+      </c>
+      <c r="F73" t="str">
+        <v>5.712</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B74" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E74" t="str">
+        <v>3</v>
+      </c>
+      <c r="F74" t="str">
+        <v>8.318</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B75" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E75" t="str">
+        <v>7</v>
+      </c>
+      <c r="F75" t="str">
+        <v>3.366</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B76" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E76" t="str">
+        <v>1</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2.950</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B77" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E77" t="str">
+        <v>1</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3.618</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B78" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E78" t="str">
+        <v>11</v>
+      </c>
+      <c r="F78" t="str">
+        <v>32.879</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B79" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="D67" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E67" t="str">
-        <v>1</v>
-      </c>
-      <c r="F67" t="str">
-        <v>2.851</v>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5.650</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,10 +433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.331</v>
+        <v>4.016</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>4.916</v>
+        <v>7.087</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>7.790</v>
+        <v>8.483</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" t="str">
-        <v>7.905</v>
+        <v>18.354</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BAKLAVA</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>23.555</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="7">
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>4.545</v>
+        <v>4.705</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>3.030</v>
+        <v>9.036</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>12.197</v>
+        <v>3.341</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>5.548</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>3.400</v>
+        <v>3.120</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
-        <v>15.521</v>
+        <v>6.037</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>2.876</v>
+        <v>8.189</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -676,7 +676,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>2.929</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>5.837</v>
+        <v>9.654</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>2.992</v>
+        <v>6.212</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.775</v>
+        <v>2.890</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>3.127</v>
+        <v>8.217</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" t="str">
-        <v>14.789</v>
+        <v>10.363</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.780</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -816,7 +816,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>5.400</v>
+        <v>5.488</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>7.554</v>
+        <v>5.208</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>5.431</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.712</v>
+        <v>2.728</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>2.517</v>
+        <v>11.432</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>ESTASI</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F26" t="str">
-        <v>6.330</v>
+        <v>15.660</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>11.329</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>FRAGOLA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -956,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="F28" t="str">
-        <v>10.506</v>
+        <v>13.964</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" t="str">
-        <v>9.094</v>
+        <v>13.366</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>GIANDUIA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>3.008</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>5.372</v>
+        <v>2.947</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1033,10 +1033,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>15.196</v>
+        <v>2.831</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>2.821</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDARINO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.524</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1093,10 +1093,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>5.749</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>2.827</v>
+        <v>9.252</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F37" t="str">
-        <v>4.786</v>
+        <v>14.936</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.681</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MIRTILLO</v>
+        <v>PERA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>2.538</v>
+        <v>4.989</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1196,7 +1196,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>6.275</v>
+        <v>5.883</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F41" t="str">
-        <v>23.832</v>
+        <v>7.449</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F42" t="str">
-        <v>3.071</v>
+        <v>19.953</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>5.796</v>
+        <v>2.900</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PASSION FRUIT</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>4.673</v>
+        <v>5.991</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PERA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>5.326</v>
+        <v>5.951</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.772</v>
+        <v>5.982</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F47" t="str">
-        <v>2.467</v>
+        <v>28.271</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>3.038</v>
+        <v>5.911</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>POLLICINA</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>5.993</v>
+        <v>2.240</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1393,10 +1393,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.258</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>2.809</v>
+        <v>4.435</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.942</v>
+        <v>3.046</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>5.864</v>
+        <v>2.682</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>SEADAS</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>2.963</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>STRACCIATELLA</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>34.709</v>
+        <v>2.594</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>TIRAMISU'</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>5.601</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>UVA E NOCI</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.090</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>3.055</v>
+        <v>2.356</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>YOGURT</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>8.680</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>PENSIERO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>2.491</v>
+        <v>3.085</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>SACRIPANTE</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1613,10 +1613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>5.966</v>
+        <v>993</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1636,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>2.617</v>
+        <v>3.006</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>CARROT CAKE</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1653,10 +1653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E63" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>2.879</v>
+        <v>5.733</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1673,10 +1673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E64" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" t="str">
-        <v>3.128</v>
+        <v>2.565</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="str">
-        <v>2.848</v>
+        <v>9.827</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1716,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.322</v>
+        <v>3.109</v>
       </c>
     </row>
     <row r="67">
@@ -1724,7 +1724,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1733,10 +1733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F67" t="str">
-        <v>3.162</v>
+        <v>14.521</v>
       </c>
     </row>
     <row r="68">
@@ -1744,7 +1744,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>MONT BLANC</v>
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1753,10 +1753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E68" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>3.075</v>
+        <v>5.775</v>
       </c>
     </row>
     <row r="69">
@@ -1764,7 +1764,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>PASTIERA NAPOLETANA</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1776,212 +1776,12 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>3.128</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B70" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E70" t="str">
-        <v>1</v>
-      </c>
-      <c r="F70" t="str">
-        <v>2.853</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B71" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E71" t="str">
-        <v>2</v>
-      </c>
-      <c r="F71" t="str">
-        <v>6.171</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B72" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E72" t="str">
-        <v>2</v>
-      </c>
-      <c r="F72" t="str">
-        <v>6.641</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B73" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C73" t="str">
-        <v/>
-      </c>
-      <c r="D73" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E73" t="str">
-        <v>2</v>
-      </c>
-      <c r="F73" t="str">
-        <v>5.712</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B74" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C74" t="str">
-        <v/>
-      </c>
-      <c r="D74" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E74" t="str">
-        <v>3</v>
-      </c>
-      <c r="F74" t="str">
-        <v>8.318</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B75" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E75" t="str">
-        <v>7</v>
-      </c>
-      <c r="F75" t="str">
-        <v>3.366</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B76" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
-      </c>
-      <c r="C76" t="str">
-        <v/>
-      </c>
-      <c r="D76" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E76" t="str">
-        <v>1</v>
-      </c>
-      <c r="F76" t="str">
-        <v>2.950</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B77" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E77" t="str">
-        <v>1</v>
-      </c>
-      <c r="F77" t="str">
-        <v>3.618</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B78" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E78" t="str">
-        <v>11</v>
-      </c>
-      <c r="F78" t="str">
-        <v>32.879</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C79" t="str">
-        <v/>
-      </c>
-      <c r="D79" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E79" t="str">
-        <v>2</v>
-      </c>
-      <c r="F79" t="str">
-        <v>5.650</v>
+        <v>2.758</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -424,7 +424,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>AMARENA</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -433,10 +433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>4.016</v>
+        <v>2.439</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>7.087</v>
+        <v>5.440</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>8.483</v>
+        <v>3.461</v>
       </c>
     </row>
     <row r="5">
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="str">
-        <v>18.354</v>
+        <v>30.049</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BAKLAVA</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="str">
-        <v>2.862</v>
+        <v>6.362</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>4.705</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>9.036</v>
+        <v>8.751</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -576,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>3.341</v>
+        <v>2.696</v>
       </c>
     </row>
     <row r="10">
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>5.208</v>
+        <v>5.483</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL PIMENTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="str">
-        <v>3.120</v>
+        <v>11.679</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="str">
-        <v>6.037</v>
+        <v>12.121</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>8.189</v>
+        <v>8.750</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>3.311</v>
+        <v>5.700</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -696,7 +696,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>9.654</v>
+        <v>7.782</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -716,7 +716,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>6.212</v>
+        <v>5.448</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>2.890</v>
+        <v>5.560</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>8.217</v>
+        <v>5.340</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>10.363</v>
+        <v>2.860</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="str">
-        <v>2.731</v>
+        <v>2.734</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="str">
-        <v>5.488</v>
+        <v>16.709</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
-        <v>5.208</v>
+        <v>13.466</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>2.702</v>
+        <v>7.116</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.728</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>11.432</v>
+        <v>4.457</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F26" t="str">
-        <v>15.660</v>
+        <v>7.804</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>LIMONE</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27" t="str">
-        <v>2.457</v>
+        <v>11.679</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>13.964</v>
+        <v>2.686</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMONE</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>13.366</v>
+        <v>6.016</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.735</v>
+        <v>2.987</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>2.947</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1033,10 +1033,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.831</v>
+        <v>5.627</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F33" t="str">
-        <v>2.757</v>
+        <v>12.035</v>
       </c>
     </row>
     <row r="34">
@@ -1076,7 +1076,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>4.962</v>
+        <v>4.893</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MIRTILLO</v>
+        <v>MELONE</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.835</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MOJITO ALLA AMARENA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>9.252</v>
+        <v>2.359</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>NOCCIOLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>14.936</v>
+        <v>9.332</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F38" t="str">
-        <v>3.065</v>
+        <v>17.449</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>4.989</v>
+        <v>2.906</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.883</v>
+        <v>2.874</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>7.449</v>
+        <v>2.452</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PERA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>19.953</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>POLLICINA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.900</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>5.991</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.951</v>
+        <v>2.137</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>SEADAS</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.982</v>
+        <v>5.808</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>STRACCIATELLA</v>
+        <v>SEADAS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>28.271</v>
+        <v>2.980</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>TIRAMISU'</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F48" t="str">
-        <v>5.911</v>
+        <v>27.744</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>UVA E NOCI</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.240</v>
+        <v>2.789</v>
       </c>
     </row>
     <row r="50">
@@ -1393,10 +1393,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.766</v>
+        <v>2.731</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>PENSIERO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="str">
-        <v>4.435</v>
+        <v>8.984</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SACRIPANTE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>3.046</v>
+        <v>2.254</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.682</v>
+        <v>6.131</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>CARROT CAKE</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>2.765</v>
+        <v>5.805</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>2.594</v>
+        <v>5.615</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F56" t="str">
-        <v>3.114</v>
+        <v>16.969</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>MONT BLANC</v>
+        <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>3.102</v>
+        <v>2.225</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>2.356</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>2.708</v>
+        <v>6.070</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>COCCO</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.085</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>TORTA CAPRESE</v>
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>993</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" t="str">
-        <v>3.006</v>
+        <v>6.080</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>EVERGREEN  BRONTE VEGAN</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1656,7 +1656,7 @@
         <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>5.733</v>
+        <v>6.454</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>CASTAGNA AL WHISKY</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1673,10 +1673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E64" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.565</v>
+        <v>2.905</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>9.827</v>
+        <v>2.698</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1713,10 +1713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F66" t="str">
-        <v>3.109</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="67">
@@ -1724,7 +1724,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1733,10 +1733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F67" t="str">
-        <v>14.521</v>
+        <v>5.919</v>
       </c>
     </row>
     <row r="68">
@@ -1744,7 +1744,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1753,10 +1753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E68" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F68" t="str">
-        <v>5.775</v>
+        <v>22.823</v>
       </c>
     </row>
     <row r="69">
@@ -1776,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.758</v>
+        <v>3.190</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
         <v>Stock</v>
       </c>
       <c r="B2" t="str">
-        <v>ANANAS E ZENZERO</v>
+        <v>AMARENA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.439</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>Stock</v>
       </c>
       <c r="B3" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ANANAS E ZENZERO</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>5.440</v>
+        <v>7.472</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>3.461</v>
+        <v>7.948</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>30.049</v>
+        <v>10.754</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>6.362</v>
+        <v>26.282</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>6.132</v>
+        <v>4.333</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BIANCANEVE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>8.751</v>
+        <v>8.470</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CAFFE'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>2.696</v>
+        <v>8.134</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>5.483</v>
+        <v>5.158</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>11.679</v>
+        <v>3.482</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <v>12.121</v>
+        <v>14.212</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>8.750</v>
+        <v>7.744</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>5.700</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>7.782</v>
+        <v>12.419</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="str">
-        <v>5.448</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>5.560</v>
+        <v>5.319</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>5.340</v>
+        <v>7.328</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.860</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>2.734</v>
+        <v>5.388</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>16.709</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>13.466</v>
+        <v>5.459</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>7.116</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>GIANDUIA</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>3.158</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" t="str">
-        <v>4.457</v>
+        <v>13.484</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F26" t="str">
-        <v>7.804</v>
+        <v>13.432</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>LIMONE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>11.679</v>
+        <v>9.271</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -956,7 +956,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>2.686</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>6.016</v>
+        <v>6.519</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.987</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" t="str">
-        <v>3.014</v>
+        <v>12.282</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1033,10 +1033,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E32" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>5.627</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>12.035</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>4.893</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MELONE</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1093,10 +1093,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.572</v>
+        <v>6.111</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MOJITO ALLA AMARENA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1116,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>2.359</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>9.332</v>
+        <v>2.509</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>NOCCIOLA</v>
+        <v>MELONE</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>17.449</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MORA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.906</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="str">
-        <v>2.874</v>
+        <v>8.818</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PASSION FRUIT</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F41" t="str">
-        <v>2.452</v>
+        <v>17.373</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1236,7 +1236,7 @@
         <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>5.009</v>
+        <v>6.043</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.542</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>POLLICINA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>5.595</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.137</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PERA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.808</v>
+        <v>4.971</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SEADAS</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>2.980</v>
+        <v>5.590</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F48" t="str">
-        <v>27.744</v>
+        <v>32.276</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>TIRAMISU'</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.789</v>
+        <v>2.418</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>YOGURT</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1393,10 +1393,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.731</v>
+        <v>5.670</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>8.984</v>
+        <v>2.503</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>PENSIERO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1436,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.254</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>SACRIPANTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F53" t="str">
-        <v>6.131</v>
+        <v>31.117</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>5.805</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>YOGURT</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>5.615</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>16.969</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1533,10 +1533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E57" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="str">
-        <v>2.225</v>
+        <v>4.684</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1553,10 +1553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>3.158</v>
+        <v>7.920</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>MONT BLANC</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" t="str">
-        <v>6.070</v>
+        <v>8.344</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>COCCO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>3.195</v>
+        <v>2.832</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1613,10 +1613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F61" t="str">
-        <v>2.142</v>
+        <v>20.371</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>6.080</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1653,10 +1653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E63" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>6.454</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.905</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1696,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>2.698</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1713,10 +1713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>4.212</v>
+        <v>2.897</v>
       </c>
     </row>
     <row r="67">
@@ -1724,7 +1724,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1733,10 +1733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>5.919</v>
+        <v>992</v>
       </c>
     </row>
     <row r="68">
@@ -1744,7 +1744,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1753,10 +1753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E68" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F68" t="str">
-        <v>22.823</v>
+        <v>5.421</v>
       </c>
     </row>
     <row r="69">
@@ -1764,24 +1764,84 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2</v>
+      </c>
+      <c r="F69" t="str">
+        <v>5.181</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E70" t="str">
+        <v>8</v>
+      </c>
+      <c r="F70" t="str">
+        <v>4.276</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>6.620</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
         <v>ZABAIONE NEW</v>
       </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="D69" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E69" t="str">
-        <v>1</v>
-      </c>
-      <c r="F69" t="str">
-        <v>3.190</v>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" t="str">
+        <v>6.103</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F72"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.125</v>
+        <v>2.114</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>7.472</v>
+        <v>4.939</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ANGURIA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>7.948</v>
+        <v>26.587</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>10.754</v>
+        <v>2.094</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>26.282</v>
+        <v>5.577</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BANANA E LIME</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>4.333</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>8.470</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BIANCANEVE</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>8.134</v>
+        <v>3.443</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CAFFE'</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>5.158</v>
+        <v>7.424</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>3.482</v>
+        <v>6.053</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>14.212</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="13">
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>7.744</v>
+        <v>2.580</v>
       </c>
     </row>
     <row r="14">
@@ -676,7 +676,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>3.000</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="15">
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>12.419</v>
+        <v>9.110</v>
       </c>
     </row>
     <row r="16">
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="str">
-        <v>11.796</v>
+        <v>8.765</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO ROSEMARY</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>5.319</v>
+        <v>3.102</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -756,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>7.328</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>2.754</v>
+        <v>5.094</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>5.388</v>
+        <v>10.138</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -816,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>2.352</v>
+        <v>2.677</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>5.459</v>
+        <v>2.633</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA VANIGLIA</v>
+        <v>ESTASI</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>7.485</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>2.626</v>
+        <v>11.119</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>13.484</v>
+        <v>12.893</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRAGOLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26" t="str">
-        <v>13.432</v>
+        <v>7.201</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>9.271</v>
+        <v>3.199</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>GIANDUIA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -956,7 +956,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>3.090</v>
+        <v>2.056</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>6.519</v>
+        <v>8.377</v>
       </c>
     </row>
     <row r="30">
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.499</v>
+        <v>2.476</v>
       </c>
     </row>
     <row r="31">
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" t="str">
-        <v>12.282</v>
+        <v>10.383</v>
       </c>
     </row>
     <row r="32">
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>3.077</v>
+        <v>2.993</v>
       </c>
     </row>
     <row r="33">
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>2.735</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="34">
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>2.873</v>
+        <v>5.561</v>
       </c>
     </row>
     <row r="35">
@@ -1093,10 +1093,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>6.111</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" t="str">
-        <v>2.567</v>
+        <v>14.701</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.509</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELONE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.624</v>
+        <v>5.992</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MORA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F39" t="str">
-        <v>2.319</v>
+        <v>14.681</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>PERA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>8.818</v>
+        <v>5.196</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41" t="str">
-        <v>17.373</v>
+        <v>2.850</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>6.043</v>
+        <v>2.771</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.664</v>
+        <v>2.166</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PAPAYA</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="str">
-        <v>2.651</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PASSION FRUIT</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>2.444</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PERA</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>4.971</v>
+        <v>5.823</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="str">
-        <v>5.590</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F48" t="str">
-        <v>32.276</v>
+        <v>27.870</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.418</v>
+        <v>2.860</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1393,10 +1393,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.670</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>2.503</v>
+        <v>5.220</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>SEADAS</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1433,10 +1433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.892</v>
+        <v>5.282</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>STRACCIATELLA</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>31.117</v>
+        <v>2.732</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>UVA E NOCI</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54" t="str">
-        <v>2.522</v>
+        <v>14.270</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>YOGURT</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>2.805</v>
+        <v>2.634</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="str">
-        <v>3.014</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>PENSIERO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1533,10 +1533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E57" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>4.684</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1553,10 +1553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>7.920</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>8.344</v>
+        <v>2.809</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>CARROT CAKE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1593,10 +1593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="str">
-        <v>2.832</v>
+        <v>5.426</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1613,10 +1613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E61" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>20.371</v>
+        <v>2.928</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F62" t="str">
-        <v>2.592</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.681</v>
+        <v>2.954</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>SUSHI VEGANO</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1673,10 +1673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E64" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F64" t="str">
-        <v>250</v>
+        <v>23.481</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>CIOCCOLATO AL WHISKY</v>
+        <v>ZABAIONE NEW</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="str">
-        <v>3.125</v>
+        <v>5.828</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1716,132 +1716,12 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.897</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B67" t="str">
-        <v>TORTA CAPRESE</v>
-      </c>
-      <c r="C67" t="str">
-        <v/>
-      </c>
-      <c r="D67" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E67" t="str">
-        <v>1</v>
-      </c>
-      <c r="F67" t="str">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B68" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E68" t="str">
-        <v>2</v>
-      </c>
-      <c r="F68" t="str">
-        <v>5.421</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B69" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C69" t="str">
-        <v/>
-      </c>
-      <c r="D69" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E69" t="str">
-        <v>2</v>
-      </c>
-      <c r="F69" t="str">
-        <v>5.181</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B70" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C70" t="str">
-        <v/>
-      </c>
-      <c r="D70" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E70" t="str">
-        <v>8</v>
-      </c>
-      <c r="F70" t="str">
-        <v>4.276</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B71" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C71" t="str">
-        <v/>
-      </c>
-      <c r="D71" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E71" t="str">
-        <v>2</v>
-      </c>
-      <c r="F71" t="str">
-        <v>6.620</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B72" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E72" t="str">
-        <v>2</v>
-      </c>
-      <c r="F72" t="str">
-        <v>6.103</v>
+        <v>2.973</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,10 +433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>2.114</v>
+        <v>4.480</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>4.939</v>
+        <v>2.531</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F4" t="str">
-        <v>26.587</v>
+        <v>5.734</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BANANA E LIME</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F5" t="str">
-        <v>2.094</v>
+        <v>23.182</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -516,7 +516,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>5.577</v>
+        <v>4.142</v>
       </c>
     </row>
     <row r="7">
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="str">
-        <v>2.769</v>
+        <v>8.594</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="str">
-        <v>8.368</v>
+        <v>5.314</v>
       </c>
     </row>
     <row r="9">
@@ -576,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>3.443</v>
+        <v>3.486</v>
       </c>
     </row>
     <row r="10">
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>7.424</v>
+        <v>2.401</v>
       </c>
     </row>
     <row r="11">
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>6.053</v>
+        <v>6.267</v>
       </c>
     </row>
     <row r="12">
@@ -636,7 +636,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.048</v>
+        <v>2.858</v>
       </c>
     </row>
     <row r="13">
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>2.580</v>
+        <v>5.101</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="str">
-        <v>2.988</v>
+        <v>5.891</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>9.110</v>
+        <v>5.864</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>8.765</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO ROSEMARY</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>3.102</v>
+        <v>2.317</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>8.416</v>
+        <v>4.819</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="str">
-        <v>5.094</v>
+        <v>8.422</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA AGNESE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>10.138</v>
+        <v>8.975</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>2.677</v>
+        <v>7.021</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>2.633</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>ESTASI</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>8.532</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>FIORDILATTE</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>11.119</v>
+        <v>2.461</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>FRAGOLA</v>
+        <v>LIMONE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>12.893</v>
+        <v>10.020</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>7.201</v>
+        <v>2.952</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>GIANDUIA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>3.199</v>
+        <v>3.239</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>LAMPONI SORBETTO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -956,7 +956,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>2.056</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>MORA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>8.377</v>
+        <v>2.275</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LEMON CURD</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="str">
-        <v>2.476</v>
+        <v>5.954</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>LIMONE</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="str">
-        <v>10.383</v>
+        <v>9.041</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.993</v>
+        <v>2.891</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>5.498</v>
+        <v>2.170</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>PERA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>5.561</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.805</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>14.701</v>
+        <v>8.528</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MIRTILLO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.487</v>
+        <v>2.676</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.992</v>
+        <v>2.691</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>NOCCIOLA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="str">
-        <v>14.681</v>
+        <v>21.697</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PERA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.196</v>
+        <v>2.647</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>PERE BELLE HELENE</v>
+        <v>YOGURT</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>2.850</v>
+        <v>5.804</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>ZABAIONE GELATO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1236,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>2.771</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.166</v>
+        <v>2.459</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>5.962</v>
+        <v>8.762</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.518</v>
+        <v>5.387</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="F46" t="str">
-        <v>5.823</v>
+        <v>5.300</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>SEADAS</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="str">
-        <v>3.045</v>
+        <v>8.792</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>STRACCIATELLA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>27.870</v>
+        <v>2.677</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>YOGURT</v>
+        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.860</v>
+        <v>2.803</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>PENSIERO</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1393,10 +1393,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>2.702</v>
+        <v>6.087</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>5.220</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1433,10 +1433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F52" t="str">
-        <v>5.282</v>
+        <v>2.608</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>CARROT CAKE</v>
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1456,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>2.732</v>
+        <v>3.232</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
-        <v>14.270</v>
+        <v>5.569</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F55" t="str">
-        <v>2.634</v>
+        <v>19.968</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>STRAWBERRY FIELD FOREVER</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,215 +1513,15 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>5.403</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B57" t="str">
-        <v>MONT BLANC</v>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E57" t="str">
-        <v>1</v>
-      </c>
-      <c r="F57" t="str">
-        <v>3.090</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B58" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E58" t="str">
-        <v>1</v>
-      </c>
-      <c r="F58" t="str">
-        <v>2.958</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B59" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E59" t="str">
-        <v>1</v>
-      </c>
-      <c r="F59" t="str">
-        <v>2.809</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B60" t="str">
-        <v>SACHER TORTE</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E60" t="str">
-        <v>2</v>
-      </c>
-      <c r="F60" t="str">
-        <v>5.426</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B61" t="str">
-        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E61" t="str">
-        <v>1</v>
-      </c>
-      <c r="F61" t="str">
-        <v>2.928</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B62" t="str">
-        <v>CREMA MASCARPONE</v>
-      </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="D62" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E62" t="str">
-        <v>6</v>
-      </c>
-      <c r="F62" t="str">
-        <v>3.202</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B63" t="str">
-        <v>COCONUT RICE CAKE</v>
-      </c>
-      <c r="C63" t="str">
-        <v/>
-      </c>
-      <c r="D63" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E63" t="str">
-        <v>1</v>
-      </c>
-      <c r="F63" t="str">
-        <v>2.954</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B64" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
-      </c>
-      <c r="C64" t="str">
-        <v/>
-      </c>
-      <c r="D64" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E64" t="str">
-        <v>8</v>
-      </c>
-      <c r="F64" t="str">
-        <v>23.481</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ZABAIONE NEW</v>
-      </c>
-      <c r="C65" t="str">
-        <v/>
-      </c>
-      <c r="D65" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E65" t="str">
-        <v>2</v>
-      </c>
-      <c r="F65" t="str">
-        <v>5.828</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Stock</v>
-      </c>
-      <c r="B66" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
-      </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="D66" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E66" t="str">
-        <v>1</v>
-      </c>
-      <c r="F66" t="str">
-        <v>2.973</v>
+        <v>2.834</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,7 +436,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>4.480</v>
+        <v>4.611</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>2.531</v>
+        <v>4.696</v>
       </c>
     </row>
     <row r="4">
@@ -473,10 +473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E4" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>5.734</v>
+        <v>8.485</v>
       </c>
     </row>
     <row r="5">
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" t="str">
-        <v>23.182</v>
+        <v>35.866</v>
       </c>
     </row>
     <row r="6">
@@ -516,7 +516,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="str">
-        <v>4.142</v>
+        <v>4.344</v>
       </c>
     </row>
     <row r="7">
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>8.594</v>
+        <v>2.841</v>
       </c>
     </row>
     <row r="8">
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>5.314</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>3.486</v>
+        <v>11.550</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
-        <v>2.401</v>
+        <v>6.092</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>6.267</v>
+        <v>4.461</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -636,7 +636,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>2.858</v>
+        <v>3.248</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>5.101</v>
+        <v>6.037</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" t="str">
-        <v>5.891</v>
+        <v>11.541</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="str">
-        <v>5.864</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="str">
-        <v>2.769</v>
+        <v>5.101</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.317</v>
+        <v>2.466</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>4.819</v>
+        <v>5.426</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -773,10 +773,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E19" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>8.422</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>FRAGOLA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="str">
-        <v>8.975</v>
+        <v>14.494</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F21" t="str">
-        <v>7.021</v>
+        <v>13.380</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>GIANDUIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="str">
-        <v>2.929</v>
+        <v>9.248</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>2.668</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LEMON CURD</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>2.461</v>
+        <v>7.937</v>
       </c>
     </row>
     <row r="25">
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <v>10.020</v>
+        <v>15.549</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>2.952</v>
+        <v>3.150</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MANDORLA BIANCA</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="str">
-        <v>3.239</v>
+        <v>2.793</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MIRTILLO</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>2.297</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MORA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>2.275</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" t="str">
-        <v>5.954</v>
+        <v>15.812</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>NOCCIOLA</v>
+        <v>MELONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>9.041</v>
+        <v>2.294</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>MIRTILLO</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.891</v>
+        <v>2.527</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>PAPAYA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>2.170</v>
+        <v>5.660</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>PERA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F34" t="str">
-        <v>2.444</v>
+        <v>14.585</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="str">
-        <v>2.256</v>
+        <v>2.598</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>8.528</v>
+        <v>2.253</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>2.676</v>
+        <v>2.384</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PERA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>2.691</v>
+        <v>4.829</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F39" t="str">
-        <v>21.697</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>TIRAMISU'</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F40" t="str">
-        <v>2.647</v>
+        <v>25.162</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>YOGURT</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>5.804</v>
+        <v>5.674</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>ZABAIONE GELATO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>2.964</v>
+        <v>5.633</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PENSIERO</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.459</v>
+        <v>2.788</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>SACRIPANTE</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>8.762</v>
+        <v>8.010</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>SEADAS</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>5.387</v>
+        <v>2.812</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1313,10 +1313,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F46" t="str">
-        <v>5.300</v>
+        <v>29.914</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="str">
-        <v>8.792</v>
+        <v>10.792</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="str">
-        <v>2.677</v>
+        <v>2.704</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
+        <v>CIOCCOLATO WASABI</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="str">
-        <v>2.803</v>
+        <v>3.164</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
+        <v>YOGURT</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>6.087</v>
+        <v>6.149</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>SACHER TORTE</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.517</v>
+        <v>2.846</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1433,10 +1433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F52" t="str">
-        <v>2.608</v>
+        <v>2.011</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1456,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>3.232</v>
+        <v>2.588</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>5.569</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>19.968</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="56">
@@ -1504,24 +1504,284 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
+        <v>PISTACCHIO SIRIANO</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E56" t="str">
+        <v>3</v>
+      </c>
+      <c r="F56" t="str">
+        <v>8.553</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B57" t="str">
+        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E57" t="str">
+        <v>1</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2.897</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B58" t="str">
+        <v>FIOR DI CIOCCOLATO</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E58" t="str">
+        <v>1</v>
+      </c>
+      <c r="F58" t="str">
+        <v>2.866</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ROSA KARKADE E ARANCIA</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2</v>
+      </c>
+      <c r="F59" t="str">
+        <v>5.109</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B60" t="str">
+        <v>AVOCADO LIME E VINO BIANCO</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E60" t="str">
+        <v>1</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2.664</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B61" t="str">
+        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E61" t="str">
+        <v>1</v>
+      </c>
+      <c r="F61" t="str">
+        <v>2.623</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B62" t="str">
+        <v>EVERGREEN  BRONTE VEGAN</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5.737</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B63" t="str">
+        <v>CASTAGNA AL WHISKY</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E63" t="str">
+        <v>1</v>
+      </c>
+      <c r="F63" t="str">
+        <v>3.077</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B64" t="str">
+        <v>FAVE FRESCHE &amp; PECORINO</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E64" t="str">
+        <v>1</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2.928</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B65" t="str">
+        <v>LIMONE &amp; BASILICO</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E65" t="str">
+        <v>1</v>
+      </c>
+      <c r="F65" t="str">
+        <v>2.119</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B66" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E66" t="str">
+        <v>3</v>
+      </c>
+      <c r="F66" t="str">
+        <v>1.602</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B67" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E67" t="str">
+        <v>7</v>
+      </c>
+      <c r="F67" t="str">
+        <v>19.771</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E68" t="str">
+        <v>1</v>
+      </c>
+      <c r="F68" t="str">
+        <v>2.966</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B69" t="str">
         <v>STRAWBERRY FIELD FOREVER</v>
       </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v>Esaurito</v>
-      </c>
-      <c r="E56" t="str">
-        <v>1</v>
-      </c>
-      <c r="F56" t="str">
-        <v>2.834</v>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E69" t="str">
+        <v>1</v>
+      </c>
+      <c r="F69" t="str">
+        <v>2.726</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,10 +433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E2" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>4.611</v>
+        <v>2.513</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>4.696</v>
+        <v>5.034</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v>Stock</v>
       </c>
       <c r="B4" t="str">
-        <v>ARACHIDI COCCO E CIOCCOLATO</v>
+        <v>ANGURIA</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>8.485</v>
+        <v>7.547</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>Stock</v>
       </c>
       <c r="B5" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -493,10 +493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E5" t="str">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>35.866</v>
+        <v>11.259</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>BANANA E LIME</v>
+        <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>4.344</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BIANCANEVE</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F7" t="str">
-        <v>2.841</v>
+        <v>21.197</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>CAFFE'</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="str">
-        <v>2.976</v>
+        <v>9.119</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -576,7 +576,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>11.550</v>
+        <v>10.867</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -593,10 +593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E10" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>6.092</v>
+        <v>8.564</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CIOCCOLATO E ARANCIA</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="str">
-        <v>4.461</v>
+        <v>8.475</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -636,7 +636,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>3.248</v>
+        <v>3.697</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CIOCCOLATO MADAGASCAR</v>
+        <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="str">
-        <v>6.037</v>
+        <v>4.903</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="str">
-        <v>11.541</v>
+        <v>14.886</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>COCCO CREMA</v>
+        <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>8.339</v>
+        <v>3.082</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>5.101</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>2.466</v>
+        <v>3.044</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F18" t="str">
-        <v>5.426</v>
+        <v>17.773</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.455</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>FIORDILATTE</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>14.494</v>
+        <v>10.017</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>FRAGOLA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>13.380</v>
+        <v>7.901</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -833,10 +833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E22" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>9.248</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>GIANDUIA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -856,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="str">
-        <v>3.072</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="24">
@@ -864,7 +864,7 @@
         <v>Stock</v>
       </c>
       <c r="B24" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -873,10 +873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E24" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>7.937</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>LIMONE</v>
+        <v>ESTASI</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>15.549</v>
+        <v>9.571</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>LIQUIRIZIA</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" t="str">
-        <v>3.150</v>
+        <v>16.427</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>MANDORLA AL CARDAMOMO</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F27" t="str">
-        <v>2.793</v>
+        <v>15.485</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>MANDORLA E ARANCIA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>5.682</v>
+        <v>6.545</v>
       </c>
     </row>
     <row r="29">
@@ -964,7 +964,7 @@
         <v>Stock</v>
       </c>
       <c r="B29" t="str">
-        <v>MANDORLA TOSTATA</v>
+        <v>LAMPONI SORBETTO</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>2.873</v>
+        <v>6.137</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>MANGO SOLE DI SICILIA</v>
+        <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E30" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>15.812</v>
+        <v>2.800</v>
       </c>
     </row>
     <row r="31">
@@ -1004,7 +1004,7 @@
         <v>Stock</v>
       </c>
       <c r="B31" t="str">
-        <v>MELONE</v>
+        <v>LIMONE</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="str">
-        <v>2.294</v>
+        <v>8.073</v>
       </c>
     </row>
     <row r="32">
@@ -1024,7 +1024,7 @@
         <v>Stock</v>
       </c>
       <c r="B32" t="str">
-        <v>MIRTILLO</v>
+        <v>LIQUIRIZIA</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.527</v>
+        <v>2.930</v>
       </c>
     </row>
     <row r="33">
@@ -1044,7 +1044,7 @@
         <v>Stock</v>
       </c>
       <c r="B33" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -1056,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>5.660</v>
+        <v>5.991</v>
       </c>
     </row>
     <row r="34">
@@ -1064,7 +1064,7 @@
         <v>Stock</v>
       </c>
       <c r="B34" t="str">
-        <v>NOCCIOLA</v>
+        <v>MANDORLA BIANCA</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>14.585</v>
+        <v>5.679</v>
       </c>
     </row>
     <row r="35">
@@ -1084,7 +1084,7 @@
         <v>Stock</v>
       </c>
       <c r="B35" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -1093,10 +1093,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>2.598</v>
+        <v>6.013</v>
       </c>
     </row>
     <row r="36">
@@ -1104,7 +1104,7 @@
         <v>Stock</v>
       </c>
       <c r="B36" t="str">
-        <v>PAPAYA</v>
+        <v>MANDORLA TOSTATA</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>2.253</v>
+        <v>5.752</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>PASSION FRUIT</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>2.384</v>
+        <v>7.192</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>PERA</v>
+        <v>MELONE</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1156,7 +1156,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="str">
-        <v>4.829</v>
+        <v>5.027</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>MORA</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1173,10 +1173,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E39" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>7.004</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>25.162</v>
+        <v>5.760</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>POLLICINA</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41" t="str">
-        <v>5.674</v>
+        <v>14.382</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1236,7 +1236,7 @@
         <v>2</v>
       </c>
       <c r="F42" t="str">
-        <v>5.633</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="str">
-        <v>2.788</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>RISO E VANIGLIA</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1273,10 +1273,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E44" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>8.010</v>
+        <v>2.396</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>SEADAS</v>
+        <v>PERA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="str">
-        <v>2.812</v>
+        <v>6.761</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>STRACCIATELLA</v>
+        <v>PESCHE AL VINO</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1313,10 +1313,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E46" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>29.914</v>
+        <v>2.303</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>TIRAMISU'</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" t="str">
-        <v>10.792</v>
+        <v>22.949</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>VENERE ROSA</v>
+        <v>POLLICINA</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1353,10 +1353,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E48" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>2.704</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>CIOCCOLATO WASABI</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="str">
-        <v>3.164</v>
+        <v>4.436</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>YOGURT</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>2</v>
       </c>
       <c r="F50" t="str">
-        <v>6.149</v>
+        <v>5.590</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>2.846</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="52">
@@ -1424,7 +1424,7 @@
         <v>Stock</v>
       </c>
       <c r="B52" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>RISO E VANIGLIA</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -1433,10 +1433,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E52" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>2.011</v>
+        <v>5.797</v>
       </c>
     </row>
     <row r="53">
@@ -1444,7 +1444,7 @@
         <v>Stock</v>
       </c>
       <c r="B53" t="str">
-        <v>PENSIERO</v>
+        <v>SEADAS</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.588</v>
+        <v>5.859</v>
       </c>
     </row>
     <row r="54">
@@ -1464,7 +1464,7 @@
         <v>Stock</v>
       </c>
       <c r="B54" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>STRACCIATELLA</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F54" t="str">
-        <v>2.607</v>
+        <v>30.139</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>TIRAMISU'</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="str">
-        <v>5.352</v>
+        <v>8.113</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1513,10 +1513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E56" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>8.553</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
+        <v>VENERE ROSA</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.897</v>
+        <v>2.609</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>FIOR DI CIOCCOLATO</v>
+        <v>YOGURT</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1553,10 +1553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" t="str">
-        <v>2.866</v>
+        <v>8.210</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="str">
-        <v>5.109</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>MELOGRANO WONDERFUL</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1593,10 +1593,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E60" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="str">
-        <v>2.664</v>
+        <v>6.972</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>DRACARYS (dragon fruit ,fragole &amp; peperoncino)</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.623</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>EVERGREEN  BRONTE VEGAN</v>
+        <v>SACRIPANTE</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" t="str">
-        <v>5.737</v>
+        <v>8.269</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>CASTAGNA AL WHISKY</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>3.077</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>FAVE FRESCHE &amp; PECORINO</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.928</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F65" t="str">
-        <v>2.119</v>
+        <v>14.240</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1713,10 +1713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E66" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>1.602</v>
+        <v>2.462</v>
       </c>
     </row>
     <row r="67">
@@ -1724,7 +1724,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1733,10 +1733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E67" t="str">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>19.771</v>
+        <v>3.237</v>
       </c>
     </row>
     <row r="68">
@@ -1744,7 +1744,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>ZABAIONE NEW</v>
+        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.966</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="69">
@@ -1764,7 +1764,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>STRAWBERRY FIELD FOREVER</v>
+        <v>LIMONE &amp; BASILICO</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1776,12 +1776,132 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.726</v>
+        <v>2.290</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B70" t="str">
+        <v>CREMA MASCARPONE</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E70" t="str">
+        <v>4</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2.144</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B71" t="str">
+        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E71" t="str">
+        <v>1</v>
+      </c>
+      <c r="F71" t="str">
+        <v>2.915</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B72" t="str">
+        <v>COCONUT RICE CAKE</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E72" t="str">
+        <v>1</v>
+      </c>
+      <c r="F72" t="str">
+        <v>2.759</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B73" t="str">
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E73" t="str">
+        <v>5</v>
+      </c>
+      <c r="F73" t="str">
+        <v>13.854</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B74" t="str">
+        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2</v>
+      </c>
+      <c r="F74" t="str">
+        <v>5.611</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ZABAIONE NEW</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>Esaurito</v>
+      </c>
+      <c r="E75" t="str">
+        <v>1</v>
+      </c>
+      <c r="F75" t="str">
+        <v>3.211</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F75"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/shocapp_esaurito_7giorni.xlsx
+++ b/output/shocapp_esaurito_7giorni.xlsx
@@ -436,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>2.513</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E3" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="str">
-        <v>5.034</v>
+        <v>7.472</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>7.547</v>
+        <v>7.948</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="str">
-        <v>11.259</v>
+        <v>10.754</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>Stock</v>
       </c>
       <c r="B6" t="str">
-        <v>GIANDUIA VARIEGATA</v>
+        <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F6" t="str">
-        <v>3.213</v>
+        <v>29.554</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Stock</v>
       </c>
       <c r="B7" t="str">
-        <v>BACIO DEL PRINCIPE</v>
+        <v>BANANA E LIME</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -533,10 +533,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E7" t="str">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>21.197</v>
+        <v>4.333</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         <v>Stock</v>
       </c>
       <c r="B8" t="str">
-        <v>BANANA E LIME</v>
+        <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -553,10 +553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E8" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>9.119</v>
+        <v>8.470</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>Stock</v>
       </c>
       <c r="B9" t="str">
-        <v>BASILICO NOCI E MIELE</v>
+        <v>BIANCANEVE</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -573,10 +573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>10.867</v>
+        <v>8.134</v>
       </c>
     </row>
     <row r="10">
@@ -584,7 +584,7 @@
         <v>Stock</v>
       </c>
       <c r="B10" t="str">
-        <v>BIANCANEVE</v>
+        <v>CAFFE'</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -596,7 +596,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="str">
-        <v>8.564</v>
+        <v>7.966</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>Stock</v>
       </c>
       <c r="B11" t="str">
-        <v>CAFFE'</v>
+        <v>CASTAGNA E MIRTO</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E11" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>8.475</v>
+        <v>3.482</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         <v>Stock</v>
       </c>
       <c r="B12" t="str">
-        <v>CASTAGNA E MIRTO</v>
+        <v>CIOCCOLATO AL LATTE gelato</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E12" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <v>3.697</v>
+        <v>14.212</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>Stock</v>
       </c>
       <c r="B13" t="str">
-        <v>CHEESECAKE MIRTILLI</v>
+        <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -653,10 +653,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E13" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="str">
-        <v>4.903</v>
+        <v>10.324</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>Stock</v>
       </c>
       <c r="B14" t="str">
-        <v>CIOCCOLATO AL LATTE gelato</v>
+        <v>CIOCCOLATO KENTUCKY</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -673,10 +673,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E14" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>14.886</v>
+        <v>3.000</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +684,7 @@
         <v>Stock</v>
       </c>
       <c r="B15" t="str">
-        <v>CIOCCOLATO CRUDO DEL PERU'</v>
+        <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -693,10 +693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E15" t="str">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F15" t="str">
-        <v>3.082</v>
+        <v>15.493</v>
       </c>
     </row>
     <row r="16">
@@ -704,7 +704,7 @@
         <v>Stock</v>
       </c>
       <c r="B16" t="str">
-        <v>CIOCCOLATO KENTUCKY</v>
+        <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -713,10 +713,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E16" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="str">
-        <v>3.135</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>Stock</v>
       </c>
       <c r="B17" t="str">
-        <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
+        <v>COCCO CREMA</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -733,10 +733,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E17" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="str">
-        <v>3.044</v>
+        <v>5.319</v>
       </c>
     </row>
     <row r="18">
@@ -744,7 +744,7 @@
         <v>Stock</v>
       </c>
       <c r="B18" t="str">
-        <v>CIOCCOLATO VENEZUELA</v>
+        <v>CREMA  PASTICCIERA PARISI</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -753,10 +753,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E18" t="str">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F18" t="str">
-        <v>17.773</v>
+        <v>7.328</v>
       </c>
     </row>
     <row r="19">
@@ -764,7 +764,7 @@
         <v>Stock</v>
       </c>
       <c r="B19" t="str">
-        <v>COCCO CREMA</v>
+        <v>CREMA AGNESE</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="str">
-        <v>2.875</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         <v>Stock</v>
       </c>
       <c r="B20" t="str">
-        <v>CREMA  PASTICCIERA PARISI</v>
+        <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -793,10 +793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>10.017</v>
+        <v>5.388</v>
       </c>
     </row>
     <row r="21">
@@ -804,7 +804,7 @@
         <v>Stock</v>
       </c>
       <c r="B21" t="str">
-        <v>CREMA AGNESE</v>
+        <v>CREMA CANNELLA</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -813,10 +813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E21" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="str">
-        <v>7.901</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="22">
@@ -824,7 +824,7 @@
         <v>Stock</v>
       </c>
       <c r="B22" t="str">
-        <v>CREMA CANNELLA</v>
+        <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="str">
-        <v>4.975</v>
+        <v>5.459</v>
       </c>
     </row>
     <row r="23">
@@ -844,7 +844,7 @@
         <v>Stock</v>
       </c>
       <c r="B23" t="str">
-        <v>CREMA FRAGOLE E MANDORLE</v>
+        <v>CREMA VANIGLIA</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -853,10 +853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E23" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>2.708</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="24">
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="str">
-        <v>2.602</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="25">
@@ -884,7 +884,7 @@
         <v>Stock</v>
       </c>
       <c r="B25" t="str">
-        <v>ESTASI</v>
+        <v>FIORDILATTE</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -893,10 +893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E25" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="str">
-        <v>9.571</v>
+        <v>13.484</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>Stock</v>
       </c>
       <c r="B26" t="str">
-        <v>FIORDILATTE</v>
+        <v>FRAGOLA</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -913,10 +913,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E26" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" t="str">
-        <v>16.427</v>
+        <v>17.670</v>
       </c>
     </row>
     <row r="27">
@@ -924,7 +924,7 @@
         <v>Stock</v>
       </c>
       <c r="B27" t="str">
-        <v>FRAGOLA</v>
+        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -933,10 +933,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E27" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" t="str">
-        <v>15.485</v>
+        <v>9.271</v>
       </c>
     </row>
     <row r="28">
@@ -944,7 +944,7 @@
         <v>Stock</v>
       </c>
       <c r="B28" t="str">
-        <v>FRUTTI DI BOSCO(LAMPONE,RIBES,MORA,MIRTILLO)</v>
+        <v>GIANDUIA</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E28" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>6.545</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="29">
@@ -973,10 +973,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E29" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>6.137</v>
+        <v>8.575</v>
       </c>
     </row>
     <row r="30">
@@ -984,7 +984,7 @@
         <v>Stock</v>
       </c>
       <c r="B30" t="str">
-        <v>LATTE MENTA E CIOCCOLATO</v>
+        <v>LEMON CURD</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>2.800</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="31">
@@ -1013,10 +1013,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E31" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" t="str">
-        <v>8.073</v>
+        <v>14.807</v>
       </c>
     </row>
     <row r="32">
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="str">
-        <v>2.930</v>
+        <v>3.077</v>
       </c>
     </row>
     <row r="33">
@@ -1053,10 +1053,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E33" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="str">
-        <v>5.991</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="34">
@@ -1073,10 +1073,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E34" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>5.679</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="35">
@@ -1096,7 +1096,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>6.013</v>
+        <v>6.111</v>
       </c>
     </row>
     <row r="36">
@@ -1113,10 +1113,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E36" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="str">
-        <v>5.752</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="37">
@@ -1124,7 +1124,7 @@
         <v>Stock</v>
       </c>
       <c r="B37" t="str">
-        <v>MELA MANDORLA E CANNELLA</v>
+        <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1133,10 +1133,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E37" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="str">
-        <v>7.192</v>
+        <v>2.394</v>
       </c>
     </row>
     <row r="38">
@@ -1144,7 +1144,7 @@
         <v>Stock</v>
       </c>
       <c r="B38" t="str">
-        <v>MELONE</v>
+        <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -1153,10 +1153,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E38" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>5.027</v>
+        <v>2.509</v>
       </c>
     </row>
     <row r="39">
@@ -1164,7 +1164,7 @@
         <v>Stock</v>
       </c>
       <c r="B39" t="str">
-        <v>MORA</v>
+        <v>MELONE</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -1176,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="str">
-        <v>2.411</v>
+        <v>2.624</v>
       </c>
     </row>
     <row r="40">
@@ -1184,7 +1184,7 @@
         <v>Stock</v>
       </c>
       <c r="B40" t="str">
-        <v>MOU LATTE SALATO</v>
+        <v>MORA</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -1193,10 +1193,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E40" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="str">
-        <v>5.760</v>
+        <v>2.319</v>
       </c>
     </row>
     <row r="41">
@@ -1204,7 +1204,7 @@
         <v>Stock</v>
       </c>
       <c r="B41" t="str">
-        <v>NOCCIOLA</v>
+        <v>MOU LATTE SALATO</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -1213,10 +1213,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E41" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" t="str">
-        <v>14.382</v>
+        <v>8.818</v>
       </c>
     </row>
     <row r="42">
@@ -1224,7 +1224,7 @@
         <v>Stock</v>
       </c>
       <c r="B42" t="str">
-        <v>NOCCIOLA AL FRUTTOSIO</v>
+        <v>NOCCIOLA</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -1233,10 +1233,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E42" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F42" t="str">
-        <v>6.207</v>
+        <v>17.373</v>
       </c>
     </row>
     <row r="43">
@@ -1244,7 +1244,7 @@
         <v>Stock</v>
       </c>
       <c r="B43" t="str">
-        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
+        <v>NOCCIOLA AL FRUTTOSIO</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E43" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>2.507</v>
+        <v>6.043</v>
       </c>
     </row>
     <row r="44">
@@ -1264,7 +1264,7 @@
         <v>Stock</v>
       </c>
       <c r="B44" t="str">
-        <v>PASSION FRUIT</v>
+        <v>PANACEA (Latte di mandorla Menta &amp; Ginseng)</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="str">
-        <v>2.396</v>
+        <v>2.664</v>
       </c>
     </row>
     <row r="45">
@@ -1284,7 +1284,7 @@
         <v>Stock</v>
       </c>
       <c r="B45" t="str">
-        <v>PERA</v>
+        <v>PAPAYA</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -1293,10 +1293,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E45" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>6.761</v>
+        <v>2.651</v>
       </c>
     </row>
     <row r="46">
@@ -1304,7 +1304,7 @@
         <v>Stock</v>
       </c>
       <c r="B46" t="str">
-        <v>PESCHE AL VINO</v>
+        <v>PASSION FRUIT</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>2.303</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         <v>Stock</v>
       </c>
       <c r="B47" t="str">
-        <v>PISTACCHIO DI BRONTE</v>
+        <v>PERA</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -1333,10 +1333,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E47" t="str">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>22.949</v>
+        <v>4.971</v>
       </c>
     </row>
     <row r="48">
@@ -1344,7 +1344,7 @@
         <v>Stock</v>
       </c>
       <c r="B48" t="str">
-        <v>POLLICINA</v>
+        <v>PERE BELLE HELENE</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -1356,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="str">
-        <v>5.607</v>
+        <v>5.590</v>
       </c>
     </row>
     <row r="49">
@@ -1364,7 +1364,7 @@
         <v>Stock</v>
       </c>
       <c r="B49" t="str">
-        <v>PUNCH PARADISE</v>
+        <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -1373,10 +1373,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E49" t="str">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F49" t="str">
-        <v>4.436</v>
+        <v>35.047</v>
       </c>
     </row>
     <row r="50">
@@ -1384,7 +1384,7 @@
         <v>Stock</v>
       </c>
       <c r="B50" t="str">
-        <v>RICOTTA E AGRUMI</v>
+        <v>PUNCH PARADISE</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -1393,10 +1393,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E50" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>5.590</v>
+        <v>2.418</v>
       </c>
     </row>
     <row r="51">
@@ -1404,7 +1404,7 @@
         <v>Stock</v>
       </c>
       <c r="B51" t="str">
-        <v>RICOTTA, MIELE E COCCO</v>
+        <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1413,10 +1413,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>2.839</v>
+        <v>5.670</v>
       </c>
     </row>
     <row r="52">
@@ -1436,7 +1436,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="str">
-        <v>5.797</v>
+        <v>5.514</v>
       </c>
     </row>
     <row r="53">
@@ -1453,10 +1453,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E53" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="str">
-        <v>5.859</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="54">
@@ -1473,10 +1473,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E54" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F54" t="str">
-        <v>30.139</v>
+        <v>36.581</v>
       </c>
     </row>
     <row r="55">
@@ -1484,7 +1484,7 @@
         <v>Stock</v>
       </c>
       <c r="B55" t="str">
-        <v>TIRAMISU'</v>
+        <v>UVA E NOCI</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1493,10 +1493,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E55" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="str">
-        <v>8.113</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="56">
@@ -1504,7 +1504,7 @@
         <v>Stock</v>
       </c>
       <c r="B56" t="str">
-        <v>UVA E NOCI</v>
+        <v>YOGURT</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1516,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="str">
-        <v>2.444</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="57">
@@ -1524,7 +1524,7 @@
         <v>Stock</v>
       </c>
       <c r="B57" t="str">
-        <v>VENERE ROSA</v>
+        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="str">
-        <v>2.609</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="58">
@@ -1544,7 +1544,7 @@
         <v>Stock</v>
       </c>
       <c r="B58" t="str">
-        <v>YOGURT</v>
+        <v>PENSIERO</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1553,10 +1553,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E58" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" t="str">
-        <v>8.210</v>
+        <v>4.684</v>
       </c>
     </row>
     <row r="59">
@@ -1564,7 +1564,7 @@
         <v>Stock</v>
       </c>
       <c r="B59" t="str">
-        <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
+        <v>BUONGIORNO AMORE</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1573,10 +1573,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E59" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" t="str">
-        <v>2.651</v>
+        <v>7.920</v>
       </c>
     </row>
     <row r="60">
@@ -1584,7 +1584,7 @@
         <v>Stock</v>
       </c>
       <c r="B60" t="str">
-        <v>MELOGRANO WONDERFUL</v>
+        <v>TE VERDE MATCHA</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1596,7 +1596,7 @@
         <v>3</v>
       </c>
       <c r="F60" t="str">
-        <v>6.972</v>
+        <v>8.344</v>
       </c>
     </row>
     <row r="61">
@@ -1604,7 +1604,7 @@
         <v>Stock</v>
       </c>
       <c r="B61" t="str">
-        <v>PENSIERO</v>
+        <v>CARROT CAKE</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1616,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="str">
-        <v>2.658</v>
+        <v>2.832</v>
       </c>
     </row>
     <row r="62">
@@ -1624,7 +1624,7 @@
         <v>Stock</v>
       </c>
       <c r="B62" t="str">
-        <v>SACRIPANTE</v>
+        <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1633,10 +1633,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E62" t="str">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F62" t="str">
-        <v>8.269</v>
+        <v>20.371</v>
       </c>
     </row>
     <row r="63">
@@ -1644,7 +1644,7 @@
         <v>Stock</v>
       </c>
       <c r="B63" t="str">
-        <v>BUONGIORNO AMORE</v>
+        <v>ROSA KARKADE E ARANCIA</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="str">
-        <v>2.863</v>
+        <v>2.592</v>
       </c>
     </row>
     <row r="64">
@@ -1664,7 +1664,7 @@
         <v>Stock</v>
       </c>
       <c r="B64" t="str">
-        <v>TE VERDE MATCHA</v>
+        <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="str">
-        <v>2.576</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="65">
@@ -1684,7 +1684,7 @@
         <v>Stock</v>
       </c>
       <c r="B65" t="str">
-        <v>PISTACCHIO SIRIANO</v>
+        <v>SUSHI VEGANO</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1693,10 +1693,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E65" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65" t="str">
-        <v>14.240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66">
@@ -1704,7 +1704,7 @@
         <v>Stock</v>
       </c>
       <c r="B66" t="str">
-        <v>ROSA KARKADE E ARANCIA</v>
+        <v>CIOCCOLATO AL WHISKY</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1716,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>2.462</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="67">
@@ -1724,7 +1724,7 @@
         <v>Stock</v>
       </c>
       <c r="B67" t="str">
-        <v>AVOCADO LIME E VINO BIANCO</v>
+        <v>MONT BLANC</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="str">
-        <v>3.237</v>
+        <v>3.090</v>
       </c>
     </row>
     <row r="68">
@@ -1744,7 +1744,7 @@
         <v>Stock</v>
       </c>
       <c r="B68" t="str">
-        <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
+        <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="str">
-        <v>2.271</v>
+        <v>2.897</v>
       </c>
     </row>
     <row r="69">
@@ -1764,7 +1764,7 @@
         <v>Stock</v>
       </c>
       <c r="B69" t="str">
-        <v>LIMONE &amp; BASILICO</v>
+        <v>TORTA CAPRESE</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="str">
-        <v>2.290</v>
+        <v>992</v>
       </c>
     </row>
     <row r="70">
@@ -1784,7 +1784,7 @@
         <v>Stock</v>
       </c>
       <c r="B70" t="str">
-        <v>CREMA MASCARPONE</v>
+        <v>SACHER TORTE</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1793,10 +1793,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E70" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70" t="str">
-        <v>2.144</v>
+        <v>5.421</v>
       </c>
     </row>
     <row r="71">
@@ -1804,7 +1804,7 @@
         <v>Stock</v>
       </c>
       <c r="B71" t="str">
-        <v>BANACHI, BANANA ARACHIDI &amp; CARAMELLO</v>
+        <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -1813,10 +1813,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E71" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" t="str">
-        <v>2.915</v>
+        <v>5.181</v>
       </c>
     </row>
     <row r="72">
@@ -1824,7 +1824,7 @@
         <v>Stock</v>
       </c>
       <c r="B72" t="str">
-        <v>COCONUT RICE CAKE</v>
+        <v>CREMA MASCARPONE</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -1833,10 +1833,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E72" t="str">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F72" t="str">
-        <v>2.759</v>
+        <v>4.276</v>
       </c>
     </row>
     <row r="73">
@@ -1844,7 +1844,7 @@
         <v>Stock</v>
       </c>
       <c r="B73" t="str">
-        <v>PISTACCHIO LARNAKA , CIPRO</v>
+        <v>COCONUT RICE CAKE</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -1853,10 +1853,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E73" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F73" t="str">
-        <v>13.854</v>
+        <v>6.620</v>
       </c>
     </row>
     <row r="74">
@@ -1864,7 +1864,7 @@
         <v>Stock</v>
       </c>
       <c r="B74" t="str">
-        <v>CIOCCOLATO  UGANDA PERLA D'AFRICA</v>
+        <v>PISTACCHIO LARNAKA , CIPRO</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1873,10 +1873,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E74" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>5.611</v>
+        <v>2.793</v>
       </c>
     </row>
     <row r="75">
@@ -1893,10 +1893,10 @@
         <v>Esaurito</v>
       </c>
       <c r="E75" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="str">
-        <v>3.211</v>
+        <v>6.103</v>
       </c>
     </row>
   </sheetData>
